--- a/test-data/tenant-config-packages/tc-tenant-config-package-test.xlsx
+++ b/test-data/tenant-config-packages/tc-tenant-config-package-test.xlsx
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>{"url":"http://mockserver:1080/tc/ingest","method":"POST","tokenHeader":"X-API-Token"}</t>
+          <t>{"target_endpoint":"http://mockserver:1080/tc/ingest"}</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
